--- a/DateBase/orders/Nhat 48_2026-10-12.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-12.xlsx
@@ -521,6 +521,9 @@
       <c r="C11" t="str">
         <v>302_彩星 浅粉_Tinted Gypso light pink_undefined_0.5kg</v>
       </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -579,7 +582,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0333501510551170</v>
+        <v>0333501510551171</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-12.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -522,12 +522,95 @@
         <v>302_彩星 浅粉_Tinted Gypso light pink_undefined_0.5kg</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>87_紫霞非洲菊_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3</v>
+      </c>
+      <c r="C18" t="str">
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>4</v>
+      </c>
+      <c r="C19" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>155_曼塔_Menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0333501510551171</v>
+        <v>033350151055117151833535315100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-12.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-12.xlsx
@@ -607,6 +607,9 @@
       <c r="C21" t="str">
         <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
       </c>
+      <c r="F21" t="str">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -665,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>033350151055117151833535315100</v>
+        <v>0333501510551171518335353151030</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-12.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,9 +611,33 @@
         <v>30</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>200_粉佳人_Nirvana_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L24"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -668,7 +692,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0333501510551171518335353151030</v>
+        <v>03335015105511715183353531510305235</v>
       </c>
     </row>
   </sheetData>
